--- a/parts.xlsx
+++ b/parts.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Eduardo Poço\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E0BBA58-34DD-4090-B127-42FDC7C19289}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE932182-1B51-4E23-949B-C745285051F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="23640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$3454</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -10587,7 +10590,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -10596,6 +10599,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -77135,8 +77141,8 @@
       <c r="F2549" s="2">
         <v>1000</v>
       </c>
-      <c r="G2549" s="2">
-        <v>1000</v>
+      <c r="G2549" s="4">
+        <v>305</v>
       </c>
       <c r="H2549" s="3" t="s">
         <v>3493</v>
@@ -77161,8 +77167,8 @@
       <c r="F2550" s="2">
         <v>1000</v>
       </c>
-      <c r="G2550" s="2">
-        <v>1000</v>
+      <c r="G2550" s="4">
+        <v>305</v>
       </c>
       <c r="H2550" s="3" t="s">
         <v>3493</v>
@@ -77187,8 +77193,8 @@
       <c r="F2551" s="2">
         <v>985</v>
       </c>
-      <c r="G2551" s="2">
-        <v>985</v>
+      <c r="G2551" s="4">
+        <v>230</v>
       </c>
       <c r="H2551" s="3" t="s">
         <v>3493</v>
@@ -77213,8 +77219,8 @@
       <c r="F2552" s="2">
         <v>985</v>
       </c>
-      <c r="G2552" s="2">
-        <v>985</v>
+      <c r="G2552" s="4">
+        <v>190</v>
       </c>
       <c r="H2552" s="3" t="s">
         <v>3493</v>
@@ -77239,8 +77245,8 @@
       <c r="F2553" s="2">
         <v>985</v>
       </c>
-      <c r="G2553" s="2">
-        <v>985</v>
+      <c r="G2553" s="4">
+        <v>215</v>
       </c>
       <c r="H2553" s="3" t="s">
         <v>3493</v>
@@ -77265,8 +77271,8 @@
       <c r="F2554" s="2">
         <v>1145</v>
       </c>
-      <c r="G2554" s="2">
-        <v>1145</v>
+      <c r="G2554" s="4">
+        <v>485</v>
       </c>
       <c r="H2554" s="3" t="s">
         <v>3493</v>
@@ -77291,8 +77297,8 @@
       <c r="F2555" s="2">
         <v>1145</v>
       </c>
-      <c r="G2555" s="2">
-        <v>1145</v>
+      <c r="G2555" s="4">
+        <v>485</v>
       </c>
       <c r="H2555" s="3" t="s">
         <v>3493</v>
@@ -77317,8 +77323,8 @@
       <c r="F2556" s="2">
         <v>985</v>
       </c>
-      <c r="G2556" s="2">
-        <v>985</v>
+      <c r="G2556" s="4">
+        <v>230</v>
       </c>
       <c r="H2556" s="3" t="s">
         <v>3493</v>
@@ -77343,8 +77349,8 @@
       <c r="F2557" s="2">
         <v>985</v>
       </c>
-      <c r="G2557" s="2">
-        <v>985</v>
+      <c r="G2557" s="4">
+        <v>215</v>
       </c>
       <c r="H2557" s="3" t="s">
         <v>3493</v>
@@ -77369,8 +77375,8 @@
       <c r="F2558" s="2">
         <v>985</v>
       </c>
-      <c r="G2558" s="2">
-        <v>985</v>
+      <c r="G2558" s="4">
+        <v>215</v>
       </c>
       <c r="H2558" s="3" t="s">
         <v>3493</v>
@@ -77395,8 +77401,8 @@
       <c r="F2559" s="2">
         <v>990</v>
       </c>
-      <c r="G2559" s="2">
-        <v>990</v>
+      <c r="G2559" s="4">
+        <v>210</v>
       </c>
       <c r="H2559" s="3" t="s">
         <v>3493</v>
@@ -77421,8 +77427,8 @@
       <c r="F2560" s="2">
         <v>1000</v>
       </c>
-      <c r="G2560" s="2">
-        <v>1000</v>
+      <c r="G2560" s="4">
+        <v>305</v>
       </c>
       <c r="H2560" s="3" t="s">
         <v>3493</v>
@@ -77447,8 +77453,8 @@
       <c r="F2561" s="2">
         <v>1145</v>
       </c>
-      <c r="G2561" s="2">
-        <v>1145</v>
+      <c r="G2561" s="4">
+        <v>490</v>
       </c>
       <c r="H2561" s="3" t="s">
         <v>3493</v>
@@ -77473,8 +77479,8 @@
       <c r="F2562" s="2">
         <v>990</v>
       </c>
-      <c r="G2562" s="2">
-        <v>990</v>
+      <c r="G2562" s="4">
+        <v>210</v>
       </c>
       <c r="H2562" s="3" t="s">
         <v>3493</v>
@@ -77499,8 +77505,8 @@
       <c r="F2563" s="2">
         <v>1050</v>
       </c>
-      <c r="G2563" s="2">
-        <v>1050</v>
+      <c r="G2563" s="4">
+        <v>450</v>
       </c>
       <c r="H2563" s="3" t="s">
         <v>3493</v>
@@ -77525,8 +77531,8 @@
       <c r="F2564" s="2">
         <v>990</v>
       </c>
-      <c r="G2564" s="2">
-        <v>990</v>
+      <c r="G2564" s="4">
+        <v>230</v>
       </c>
       <c r="H2564" s="3" t="s">
         <v>3493</v>
@@ -77551,8 +77557,8 @@
       <c r="F2565" s="2">
         <v>990</v>
       </c>
-      <c r="G2565" s="2">
-        <v>990</v>
+      <c r="G2565" s="4">
+        <v>190</v>
       </c>
       <c r="H2565" s="3" t="s">
         <v>3493</v>
@@ -77577,8 +77583,8 @@
       <c r="F2566" s="2">
         <v>990</v>
       </c>
-      <c r="G2566" s="2">
-        <v>990</v>
+      <c r="G2566" s="4">
+        <v>215</v>
       </c>
       <c r="H2566" s="3" t="s">
         <v>3493</v>
@@ -77603,8 +77609,8 @@
       <c r="F2567" s="2">
         <v>950</v>
       </c>
-      <c r="G2567" s="2">
-        <v>950</v>
+      <c r="G2567" s="4">
+        <v>240</v>
       </c>
       <c r="H2567" s="3" t="s">
         <v>3493</v>
@@ -77629,8 +77635,8 @@
       <c r="F2568" s="2">
         <v>950</v>
       </c>
-      <c r="G2568" s="2">
-        <v>950</v>
+      <c r="G2568" s="4">
+        <v>240</v>
       </c>
       <c r="H2568" s="3" t="s">
         <v>3493</v>
@@ -77655,8 +77661,8 @@
       <c r="F2569" s="2">
         <v>1050</v>
       </c>
-      <c r="G2569" s="2">
-        <v>1050</v>
+      <c r="G2569" s="4">
+        <v>490</v>
       </c>
       <c r="H2569" s="3" t="s">
         <v>3493</v>
@@ -77681,8 +77687,8 @@
       <c r="F2570" s="2">
         <v>990</v>
       </c>
-      <c r="G2570" s="2">
-        <v>990</v>
+      <c r="G2570" s="4">
+        <v>230</v>
       </c>
       <c r="H2570" s="3" t="s">
         <v>3493</v>
@@ -77707,8 +77713,8 @@
       <c r="F2571" s="2">
         <v>1305</v>
       </c>
-      <c r="G2571" s="2">
-        <v>1305</v>
+      <c r="G2571" s="4">
+        <v>1000</v>
       </c>
       <c r="H2571" s="3" t="s">
         <v>3493</v>
@@ -77733,8 +77739,8 @@
       <c r="F2572" s="2">
         <v>990</v>
       </c>
-      <c r="G2572" s="2">
-        <v>990</v>
+      <c r="G2572" s="4">
+        <v>240</v>
       </c>
       <c r="H2572" s="3" t="s">
         <v>3493</v>
@@ -77759,8 +77765,8 @@
       <c r="F2573" s="2">
         <v>990</v>
       </c>
-      <c r="G2573" s="2">
-        <v>990</v>
+      <c r="G2573" s="4">
+        <v>240</v>
       </c>
       <c r="H2573" s="3" t="s">
         <v>3493</v>
@@ -77785,8 +77791,8 @@
       <c r="F2574" s="2">
         <v>525</v>
       </c>
-      <c r="G2574" s="2">
-        <v>525</v>
+      <c r="G2574" s="4">
+        <v>240</v>
       </c>
       <c r="H2574" s="3" t="s">
         <v>3493</v>
@@ -77811,8 +77817,8 @@
       <c r="F2575" s="2">
         <v>525</v>
       </c>
-      <c r="G2575" s="2">
-        <v>525</v>
+      <c r="G2575" s="4">
+        <v>240</v>
       </c>
       <c r="H2575" s="3" t="s">
         <v>3493</v>
@@ -77837,8 +77843,8 @@
       <c r="F2576" s="2">
         <v>1050</v>
       </c>
-      <c r="G2576" s="2">
-        <v>1050</v>
+      <c r="G2576" s="4">
+        <v>520</v>
       </c>
       <c r="H2576" s="3" t="s">
         <v>3493</v>
@@ -77863,8 +77869,8 @@
       <c r="F2577" s="2">
         <v>485</v>
       </c>
-      <c r="G2577" s="2">
-        <v>485</v>
+      <c r="G2577" s="4">
+        <v>240</v>
       </c>
       <c r="H2577" s="3" t="s">
         <v>3493</v>
@@ -77889,8 +77895,8 @@
       <c r="F2578" s="2">
         <v>485</v>
       </c>
-      <c r="G2578" s="2">
-        <v>485</v>
+      <c r="G2578" s="4">
+        <v>240</v>
       </c>
       <c r="H2578" s="3" t="s">
         <v>3493</v>
@@ -77915,8 +77921,8 @@
       <c r="F2579" s="2">
         <v>400</v>
       </c>
-      <c r="G2579" s="2">
-        <v>400</v>
+      <c r="G2579" s="4">
+        <v>230</v>
       </c>
       <c r="H2579" s="3" t="s">
         <v>3493</v>
@@ -77941,8 +77947,8 @@
       <c r="F2580" s="2">
         <v>400</v>
       </c>
-      <c r="G2580" s="2">
-        <v>400</v>
+      <c r="G2580" s="4">
+        <v>190</v>
       </c>
       <c r="H2580" s="3" t="s">
         <v>3493</v>
@@ -77967,8 +77973,8 @@
       <c r="F2581" s="2">
         <v>400</v>
       </c>
-      <c r="G2581" s="2">
-        <v>400</v>
+      <c r="G2581" s="4">
+        <v>210</v>
       </c>
       <c r="H2581" s="3" t="s">
         <v>3493</v>
@@ -77993,8 +77999,8 @@
       <c r="F2582" s="2">
         <v>1000</v>
       </c>
-      <c r="G2582" s="2">
-        <v>1000</v>
+      <c r="G2582" s="4">
+        <v>270</v>
       </c>
       <c r="H2582" s="3" t="s">
         <v>3493</v>
@@ -78019,8 +78025,8 @@
       <c r="F2583" s="2">
         <v>1145</v>
       </c>
-      <c r="G2583" s="2">
-        <v>1145</v>
+      <c r="G2583" s="4">
+        <v>400</v>
       </c>
       <c r="H2583" s="3" t="s">
         <v>3493</v>
@@ -78045,8 +78051,8 @@
       <c r="F2584" s="2">
         <v>990</v>
       </c>
-      <c r="G2584" s="2">
-        <v>990</v>
+      <c r="G2584" s="4">
+        <v>230</v>
       </c>
       <c r="H2584" s="3" t="s">
         <v>3493</v>
@@ -78071,8 +78077,8 @@
       <c r="F2585" s="2">
         <v>990</v>
       </c>
-      <c r="G2585" s="2">
-        <v>990</v>
+      <c r="G2585" s="4">
+        <v>215</v>
       </c>
       <c r="H2585" s="3" t="s">
         <v>3493</v>
@@ -78097,8 +78103,8 @@
       <c r="F2586" s="2">
         <v>990</v>
       </c>
-      <c r="G2586" s="2">
-        <v>990</v>
+      <c r="G2586" s="4">
+        <v>215</v>
       </c>
       <c r="H2586" s="3" t="s">
         <v>3493</v>
@@ -78123,8 +78129,8 @@
       <c r="F2587" s="2">
         <v>1050</v>
       </c>
-      <c r="G2587" s="2">
-        <v>1050</v>
+      <c r="G2587" s="4">
+        <v>220</v>
       </c>
       <c r="H2587" s="3" t="s">
         <v>3493</v>
@@ -78149,8 +78155,8 @@
       <c r="F2588" s="2">
         <v>240</v>
       </c>
-      <c r="G2588" s="2">
-        <v>240</v>
+      <c r="G2588" s="4">
+        <v>220</v>
       </c>
       <c r="H2588" s="3" t="s">
         <v>3493</v>
@@ -78175,8 +78181,8 @@
       <c r="F2589" s="2">
         <v>240</v>
       </c>
-      <c r="G2589" s="2">
-        <v>240</v>
+      <c r="G2589" s="4">
+        <v>220</v>
       </c>
       <c r="H2589" s="3" t="s">
         <v>3493</v>
@@ -78201,8 +78207,8 @@
       <c r="F2590" s="2">
         <v>990</v>
       </c>
-      <c r="G2590" s="2">
-        <v>990</v>
+      <c r="G2590" s="4">
+        <v>215</v>
       </c>
       <c r="H2590" s="3" t="s">
         <v>3493</v>
@@ -78227,8 +78233,8 @@
       <c r="F2591" s="2">
         <v>1050</v>
       </c>
-      <c r="G2591" s="2">
-        <v>1050</v>
+      <c r="G2591" s="4">
+        <v>225</v>
       </c>
       <c r="H2591" s="3" t="s">
         <v>3493</v>
@@ -78253,8 +78259,8 @@
       <c r="F2592" s="2">
         <v>945</v>
       </c>
-      <c r="G2592" s="2">
-        <v>945</v>
+      <c r="G2592" s="4">
+        <v>240</v>
       </c>
       <c r="H2592" s="3" t="s">
         <v>3493</v>
@@ -78279,8 +78285,8 @@
       <c r="F2593" s="2">
         <v>1875</v>
       </c>
-      <c r="G2593" s="2">
-        <v>1875</v>
+      <c r="G2593" s="4">
+        <v>210</v>
       </c>
       <c r="H2593" s="3" t="s">
         <v>3493</v>
@@ -78305,8 +78311,8 @@
       <c r="F2594" s="2">
         <v>956</v>
       </c>
-      <c r="G2594" s="2">
-        <v>956</v>
+      <c r="G2594" s="4">
+        <v>240</v>
       </c>
       <c r="H2594" s="3" t="s">
         <v>3493</v>
@@ -78331,8 +78337,8 @@
       <c r="F2595" s="2">
         <v>990</v>
       </c>
-      <c r="G2595" s="2">
-        <v>990</v>
+      <c r="G2595" s="4">
+        <v>230</v>
       </c>
       <c r="H2595" s="3" t="s">
         <v>3493</v>
@@ -78357,8 +78363,8 @@
       <c r="F2596" s="2">
         <v>990</v>
       </c>
-      <c r="G2596" s="2">
-        <v>990</v>
+      <c r="G2596" s="4">
+        <v>215</v>
       </c>
       <c r="H2596" s="3" t="s">
         <v>3493</v>
@@ -78383,8 +78389,8 @@
       <c r="F2597" s="2">
         <v>985</v>
       </c>
-      <c r="G2597" s="2">
-        <v>985</v>
+      <c r="G2597" s="4">
+        <v>240</v>
       </c>
       <c r="H2597" s="3" t="s">
         <v>3493</v>
@@ -78409,8 +78415,8 @@
       <c r="F2598" s="2">
         <v>990</v>
       </c>
-      <c r="G2598" s="2">
-        <v>990</v>
+      <c r="G2598" s="4">
+        <v>215</v>
       </c>
       <c r="H2598" s="3" t="s">
         <v>3493</v>
@@ -78435,8 +78441,8 @@
       <c r="F2599" s="2">
         <v>725</v>
       </c>
-      <c r="G2599" s="2">
-        <v>725</v>
+      <c r="G2599" s="4">
+        <v>240</v>
       </c>
       <c r="H2599" s="3" t="s">
         <v>3493</v>
@@ -78461,8 +78467,8 @@
       <c r="F2600" s="2">
         <v>723</v>
       </c>
-      <c r="G2600" s="2">
-        <v>723</v>
+      <c r="G2600" s="4">
+        <v>240</v>
       </c>
       <c r="H2600" s="3" t="s">
         <v>3493</v>
@@ -78487,8 +78493,8 @@
       <c r="F2601" s="2">
         <v>1050</v>
       </c>
-      <c r="G2601" s="2">
-        <v>1050</v>
+      <c r="G2601" s="4">
+        <v>445</v>
       </c>
       <c r="H2601" s="3" t="s">
         <v>3493</v>
@@ -78513,8 +78519,8 @@
       <c r="F2602" s="2">
         <v>990</v>
       </c>
-      <c r="G2602" s="2">
-        <v>990</v>
+      <c r="G2602" s="4">
+        <v>215</v>
       </c>
       <c r="H2602" s="3" t="s">
         <v>3493</v>
@@ -78539,8 +78545,8 @@
       <c r="F2603" s="2">
         <v>1875</v>
       </c>
-      <c r="G2603" s="2">
-        <v>1875</v>
+      <c r="G2603" s="4">
+        <v>990</v>
       </c>
       <c r="H2603" s="3" t="s">
         <v>3493</v>
@@ -78565,8 +78571,8 @@
       <c r="F2604" s="2">
         <v>770</v>
       </c>
-      <c r="G2604" s="2">
-        <v>770</v>
+      <c r="G2604" s="4">
+        <v>240</v>
       </c>
       <c r="H2604" s="3" t="s">
         <v>3493</v>
@@ -78591,8 +78597,8 @@
       <c r="F2605" s="2">
         <v>770</v>
       </c>
-      <c r="G2605" s="2">
-        <v>770</v>
+      <c r="G2605" s="4">
+        <v>240</v>
       </c>
       <c r="H2605" s="3" t="s">
         <v>3493</v>
@@ -78617,8 +78623,8 @@
       <c r="F2606" s="2">
         <v>1050</v>
       </c>
-      <c r="G2606" s="2">
-        <v>1050</v>
+      <c r="G2606" s="4">
+        <v>270</v>
       </c>
       <c r="H2606" s="3" t="s">
         <v>3493</v>
@@ -78643,8 +78649,8 @@
       <c r="F2607" s="2">
         <v>780</v>
       </c>
-      <c r="G2607" s="2">
-        <v>780</v>
+      <c r="G2607" s="4">
+        <v>240</v>
       </c>
       <c r="H2607" s="3" t="s">
         <v>3493</v>
@@ -78669,8 +78675,8 @@
       <c r="F2608" s="2">
         <v>780</v>
       </c>
-      <c r="G2608" s="2">
-        <v>780</v>
+      <c r="G2608" s="4">
+        <v>240</v>
       </c>
       <c r="H2608" s="3" t="s">
         <v>3493</v>
@@ -78695,8 +78701,8 @@
       <c r="F2609" s="2">
         <v>1050</v>
       </c>
-      <c r="G2609" s="2">
-        <v>1050</v>
+      <c r="G2609" s="4">
+        <v>280</v>
       </c>
       <c r="H2609" s="3" t="s">
         <v>3493</v>
@@ -78721,8 +78727,8 @@
       <c r="F2610" s="2">
         <v>760</v>
       </c>
-      <c r="G2610" s="2">
-        <v>760</v>
+      <c r="G2610" s="4">
+        <v>240</v>
       </c>
       <c r="H2610" s="3" t="s">
         <v>3493</v>
@@ -78747,8 +78753,8 @@
       <c r="F2611" s="2">
         <v>760</v>
       </c>
-      <c r="G2611" s="2">
-        <v>760</v>
+      <c r="G2611" s="4">
+        <v>240</v>
       </c>
       <c r="H2611" s="3" t="s">
         <v>3493</v>
@@ -78773,8 +78779,8 @@
       <c r="F2612" s="2">
         <v>1050</v>
       </c>
-      <c r="G2612" s="2">
-        <v>1050</v>
+      <c r="G2612" s="4">
+        <v>260</v>
       </c>
       <c r="H2612" s="3" t="s">
         <v>3493</v>
@@ -78799,8 +78805,8 @@
       <c r="F2613" s="2">
         <v>1010</v>
       </c>
-      <c r="G2613" s="2">
-        <v>1010</v>
+      <c r="G2613" s="4">
+        <v>240</v>
       </c>
       <c r="H2613" s="3" t="s">
         <v>3493</v>
@@ -78825,8 +78831,8 @@
       <c r="F2614" s="2">
         <v>1875</v>
       </c>
-      <c r="G2614" s="2">
-        <v>1875</v>
+      <c r="G2614" s="4">
+        <v>855</v>
       </c>
       <c r="H2614" s="3" t="s">
         <v>3493</v>
@@ -78851,8 +78857,8 @@
       <c r="F2615" s="2">
         <v>1010</v>
       </c>
-      <c r="G2615" s="2">
-        <v>1010</v>
+      <c r="G2615" s="4">
+        <v>240</v>
       </c>
       <c r="H2615" s="3" t="s">
         <v>3493</v>
@@ -78877,8 +78883,8 @@
       <c r="F2616" s="2">
         <v>1050</v>
       </c>
-      <c r="G2616" s="2">
-        <v>1050</v>
+      <c r="G2616" s="4">
+        <v>510</v>
       </c>
       <c r="H2616" s="3" t="s">
         <v>3493</v>
@@ -78903,8 +78909,8 @@
       <c r="F2617" s="2">
         <v>510</v>
       </c>
-      <c r="G2617" s="2">
-        <v>510</v>
+      <c r="G2617" s="4">
+        <v>240</v>
       </c>
       <c r="H2617" s="3" t="s">
         <v>3493</v>
@@ -78929,8 +78935,8 @@
       <c r="F2618" s="2">
         <v>510</v>
       </c>
-      <c r="G2618" s="2">
-        <v>510</v>
+      <c r="G2618" s="4">
+        <v>240</v>
       </c>
       <c r="H2618" s="3" t="s">
         <v>3493</v>
@@ -78955,8 +78961,8 @@
       <c r="F2619" s="2">
         <v>990</v>
       </c>
-      <c r="G2619" s="2">
-        <v>990</v>
+      <c r="G2619" s="4">
+        <v>215</v>
       </c>
       <c r="H2619" s="3" t="s">
         <v>3493</v>
@@ -78981,8 +78987,8 @@
       <c r="F2620" s="2">
         <v>990</v>
       </c>
-      <c r="G2620" s="2">
-        <v>990</v>
+      <c r="G2620" s="4">
+        <v>215</v>
       </c>
       <c r="H2620" s="3" t="s">
         <v>3493</v>
@@ -79007,8 +79013,8 @@
       <c r="F2621" s="2">
         <v>710</v>
       </c>
-      <c r="G2621" s="2">
-        <v>710</v>
+      <c r="G2621" s="4">
+        <v>240</v>
       </c>
       <c r="H2621" s="3" t="s">
         <v>3493</v>
@@ -79033,8 +79039,8 @@
       <c r="F2622" s="2">
         <v>710</v>
       </c>
-      <c r="G2622" s="2">
-        <v>710</v>
+      <c r="G2622" s="4">
+        <v>240</v>
       </c>
       <c r="H2622" s="3" t="s">
         <v>3493</v>
@@ -79059,8 +79065,8 @@
       <c r="F2623" s="2">
         <v>1050</v>
       </c>
-      <c r="G2623" s="2">
-        <v>1050</v>
+      <c r="G2623" s="4">
+        <v>210</v>
       </c>
       <c r="H2623" s="3" t="s">
         <v>3493</v>
@@ -79085,8 +79091,8 @@
       <c r="F2624" s="2">
         <v>1875</v>
       </c>
-      <c r="G2624" s="2">
-        <v>1875</v>
+      <c r="G2624" s="4">
+        <v>905</v>
       </c>
       <c r="H2624" s="3" t="s">
         <v>3493</v>
@@ -79111,8 +79117,8 @@
       <c r="F2625" s="2">
         <v>810</v>
       </c>
-      <c r="G2625" s="2">
-        <v>810</v>
+      <c r="G2625" s="4">
+        <v>240</v>
       </c>
       <c r="H2625" s="3" t="s">
         <v>3493</v>
@@ -79137,8 +79143,8 @@
       <c r="F2626" s="2">
         <v>810</v>
       </c>
-      <c r="G2626" s="2">
-        <v>810</v>
+      <c r="G2626" s="4">
+        <v>240</v>
       </c>
       <c r="H2626" s="3" t="s">
         <v>3493</v>
@@ -79163,8 +79169,8 @@
       <c r="F2627" s="2">
         <v>1050</v>
       </c>
-      <c r="G2627" s="2">
-        <v>1050</v>
+      <c r="G2627" s="4">
+        <v>310</v>
       </c>
       <c r="H2627" s="3" t="s">
         <v>3493</v>
@@ -79189,8 +79195,8 @@
       <c r="F2628" s="2">
         <v>1305</v>
       </c>
-      <c r="G2628" s="2">
-        <v>1305</v>
+      <c r="G2628" s="4">
+        <v>1000</v>
       </c>
       <c r="H2628" s="3" t="s">
         <v>3493</v>
@@ -79215,8 +79221,8 @@
       <c r="F2629" s="2">
         <v>1050</v>
       </c>
-      <c r="G2629" s="2">
-        <v>1050</v>
+      <c r="G2629" s="4">
+        <v>280</v>
       </c>
       <c r="H2629" s="3" t="s">
         <v>3493</v>
@@ -79241,8 +79247,8 @@
       <c r="F2630" s="2">
         <v>990</v>
       </c>
-      <c r="G2630" s="2">
-        <v>990</v>
+      <c r="G2630" s="4">
+        <v>215</v>
       </c>
       <c r="H2630" s="3" t="s">
         <v>3493</v>
@@ -79267,8 +79273,8 @@
       <c r="F2631" s="2">
         <v>990</v>
       </c>
-      <c r="G2631" s="2">
-        <v>990</v>
+      <c r="G2631" s="4">
+        <v>215</v>
       </c>
       <c r="H2631" s="3" t="s">
         <v>3493</v>
@@ -79293,8 +79299,8 @@
       <c r="F2632" s="2">
         <v>1000</v>
       </c>
-      <c r="G2632" s="2">
-        <v>1000</v>
+      <c r="G2632" s="4">
+        <v>305</v>
       </c>
       <c r="H2632" s="3" t="s">
         <v>3493</v>
@@ -79319,8 +79325,8 @@
       <c r="F2633" s="2">
         <v>730</v>
       </c>
-      <c r="G2633" s="2">
-        <v>730</v>
+      <c r="G2633" s="4">
+        <v>240</v>
       </c>
       <c r="H2633" s="3" t="s">
         <v>3493</v>
@@ -79345,8 +79351,8 @@
       <c r="F2634" s="2">
         <v>730</v>
       </c>
-      <c r="G2634" s="2">
-        <v>730</v>
+      <c r="G2634" s="4">
+        <v>240</v>
       </c>
       <c r="H2634" s="3" t="s">
         <v>3493</v>
@@ -79371,8 +79377,8 @@
       <c r="F2635" s="2">
         <v>1050</v>
       </c>
-      <c r="G2635" s="2">
-        <v>1050</v>
+      <c r="G2635" s="4">
+        <v>230</v>
       </c>
       <c r="H2635" s="3" t="s">
         <v>3493</v>
@@ -79397,8 +79403,8 @@
       <c r="F2636" s="2">
         <v>990</v>
       </c>
-      <c r="G2636" s="2">
-        <v>990</v>
+      <c r="G2636" s="4">
+        <v>215</v>
       </c>
       <c r="H2636" s="3" t="s">
         <v>3493</v>
@@ -79423,8 +79429,8 @@
       <c r="F2637" s="2">
         <v>990</v>
       </c>
-      <c r="G2637" s="2">
-        <v>990</v>
+      <c r="G2637" s="4">
+        <v>215</v>
       </c>
       <c r="H2637" s="3" t="s">
         <v>3493</v>
@@ -79449,8 +79455,8 @@
       <c r="F2638" s="2">
         <v>990</v>
       </c>
-      <c r="G2638" s="2">
-        <v>990</v>
+      <c r="G2638" s="4">
+        <v>215</v>
       </c>
       <c r="H2638" s="3" t="s">
         <v>3493</v>
@@ -79475,8 +79481,8 @@
       <c r="F2639" s="2">
         <v>1050</v>
       </c>
-      <c r="G2639" s="2">
-        <v>1050</v>
+      <c r="G2639" s="4">
+        <v>470</v>
       </c>
       <c r="H2639" s="3" t="s">
         <v>3493</v>
@@ -79501,8 +79507,8 @@
       <c r="F2640" s="2">
         <v>470</v>
       </c>
-      <c r="G2640" s="2">
-        <v>470</v>
+      <c r="G2640" s="4">
+        <v>240</v>
       </c>
       <c r="H2640" s="3" t="s">
         <v>3493</v>
@@ -79527,8 +79533,8 @@
       <c r="F2641" s="2">
         <v>470</v>
       </c>
-      <c r="G2641" s="2">
-        <v>470</v>
+      <c r="G2641" s="4">
+        <v>240</v>
       </c>
       <c r="H2641" s="3" t="s">
         <v>3493</v>
@@ -79553,8 +79559,8 @@
       <c r="F2642" s="2">
         <v>990</v>
       </c>
-      <c r="G2642" s="2">
-        <v>990</v>
+      <c r="G2642" s="4">
+        <v>215</v>
       </c>
       <c r="H2642" s="3" t="s">
         <v>3493</v>
@@ -79579,8 +79585,8 @@
       <c r="F2643" s="2">
         <v>620</v>
       </c>
-      <c r="G2643" s="2">
-        <v>620</v>
+      <c r="G2643" s="4">
+        <v>240</v>
       </c>
       <c r="H2643" s="3" t="s">
         <v>3493</v>
@@ -79605,8 +79611,8 @@
       <c r="F2644" s="2">
         <v>620</v>
       </c>
-      <c r="G2644" s="2">
-        <v>620</v>
+      <c r="G2644" s="4">
+        <v>240</v>
       </c>
       <c r="H2644" s="3" t="s">
         <v>3493</v>
@@ -79631,8 +79637,8 @@
       <c r="F2645" s="2">
         <v>1204</v>
       </c>
-      <c r="G2645" s="2">
-        <v>1204</v>
+      <c r="G2645" s="4">
+        <v>1000</v>
       </c>
       <c r="H2645" s="3" t="s">
         <v>3493</v>
@@ -79657,8 +79663,8 @@
       <c r="F2646" s="2">
         <v>1050</v>
       </c>
-      <c r="G2646" s="2">
-        <v>1050</v>
+      <c r="G2646" s="4">
+        <v>620</v>
       </c>
       <c r="H2646" s="3" t="s">
         <v>3493</v>
@@ -79683,8 +79689,8 @@
       <c r="F2647" s="2">
         <v>990</v>
       </c>
-      <c r="G2647" s="2">
-        <v>990</v>
+      <c r="G2647" s="4">
+        <v>240</v>
       </c>
       <c r="H2647" s="3" t="s">
         <v>3493</v>
@@ -79709,8 +79715,8 @@
       <c r="F2648" s="2">
         <v>990</v>
       </c>
-      <c r="G2648" s="2">
-        <v>990</v>
+      <c r="G2648" s="4">
+        <v>240</v>
       </c>
       <c r="H2648" s="3" t="s">
         <v>3493</v>
@@ -79735,8 +79741,8 @@
       <c r="F2649" s="2">
         <v>1050</v>
       </c>
-      <c r="G2649" s="2">
-        <v>1050</v>
+      <c r="G2649" s="4">
+        <v>530</v>
       </c>
       <c r="H2649" s="3" t="s">
         <v>3493</v>
@@ -79761,8 +79767,8 @@
       <c r="F2650" s="2">
         <v>450</v>
       </c>
-      <c r="G2650" s="2">
-        <v>450</v>
+      <c r="G2650" s="4">
+        <v>230</v>
       </c>
       <c r="H2650" s="3" t="s">
         <v>3493</v>
@@ -79787,8 +79793,8 @@
       <c r="F2651" s="2">
         <v>450</v>
       </c>
-      <c r="G2651" s="2">
-        <v>450</v>
+      <c r="G2651" s="4">
+        <v>190</v>
       </c>
       <c r="H2651" s="3" t="s">
         <v>3493</v>
@@ -79813,8 +79819,8 @@
       <c r="F2652" s="2">
         <v>450</v>
       </c>
-      <c r="G2652" s="2">
-        <v>450</v>
+      <c r="G2652" s="4">
+        <v>210</v>
       </c>
       <c r="H2652" s="3" t="s">
         <v>3493</v>
@@ -79839,8 +79845,8 @@
       <c r="F2653" s="2">
         <v>1145</v>
       </c>
-      <c r="G2653" s="2">
-        <v>1145</v>
+      <c r="G2653" s="4">
+        <v>450</v>
       </c>
       <c r="H2653" s="3" t="s">
         <v>3493</v>
@@ -79865,8 +79871,8 @@
       <c r="F2654" s="2">
         <v>1000</v>
       </c>
-      <c r="G2654" s="2">
-        <v>1000</v>
+      <c r="G2654" s="4">
+        <v>305</v>
       </c>
       <c r="H2654" s="3" t="s">
         <v>3493</v>
@@ -79891,8 +79897,8 @@
       <c r="F2655" s="2">
         <v>1000</v>
       </c>
-      <c r="G2655" s="2">
-        <v>1000</v>
+      <c r="G2655" s="4">
+        <v>305</v>
       </c>
       <c r="H2655" s="3" t="s">
         <v>3493</v>
@@ -100633,6 +100639,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:H3454" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
